--- a/02table/TableS10_TWAS_results.xlsx
+++ b/02table/TableS10_TWAS_results.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="11113"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEB94A12-7FB8-1B4A-99FF-AC47578BCE76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D6DFB65-9292-2F41-B34A-9B9F72B9F91F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="35060" yWindow="800" windowWidth="30240" windowHeight="17200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -724,7 +724,7 @@
     <t>FW, fresh weight; ADW, average dry weight; ML, mesocotyl length; RL, root length; SL, seedling length; pSL, partial seedling length; TL, total length.</t>
   </si>
   <si>
-    <t>Table S10 Transcriptome-wide association studies for seedling trait per se and their heterosis.</t>
+    <t>Table S10. Transcriptome-wide association studies for seedling trait per se and their heterosis.</t>
   </si>
 </sst>
 </file>
